--- a/site/Dayforce-Candidates-to-Entra-ID-Integration-Guide/headings.xlsx
+++ b/site/Dayforce-Candidates-to-Entra-ID-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D38"/>
+  <dimension ref="A1:D39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -771,29 +771,29 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Attribute Mapping</t>
+          <t>Log Insights</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>h_01K62WHC9HCCXXGMBN1YD1NZGK</t>
+          <t>h_01KMJ7X392WQQCA0H6HDPENJVT</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Candidates-to-Entra-ID-Integration-Guide/#h_01K62WHC9HCCXXGMBN1YD1NZGK</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Candidates-to-Entra-ID-Integration-Guide/#h_01KMJ7X392WQQCA0H6HDPENJVT</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Tables</t>
+          <t>Attribute Mapping</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -803,85 +803,85 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>h_01KE9K5GSK270WYMMTJ4KZHW18</t>
+          <t>h_01K62WHC9HCCXXGMBN1YD1NZGK</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Candidates-to-Entra-ID-Integration-Guide/#h_01KE9K5GSK270WYMMTJ4KZHW18</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Candidates-to-Entra-ID-Integration-Guide/#h_01K62WHC9HCCXXGMBN1YD1NZGK</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Available Tables</t>
+          <t>Tables</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H1</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>h_01KE9J91KMYQS0VZA38JDS2YRB</t>
+          <t>h_01KE9K5GSK270WYMMTJ4KZHW18</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Candidates-to-Entra-ID-Integration-Guide/#h_01KE9J91KMYQS0VZA38JDS2YRB</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Candidates-to-Entra-ID-Integration-Guide/#h_01KE9K5GSK270WYMMTJ4KZHW18</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Location To Domain Table</t>
+          <t>Available Tables</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>h_01KE9J91KMC68FBV8GSV3SW9P2</t>
+          <t>h_01KE9J91KMYQS0VZA38JDS2YRB</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Candidates-to-Entra-ID-Integration-Guide/#h_01KE9J91KMC68FBV8GSV3SW9P2</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Candidates-to-Entra-ID-Integration-Guide/#h_01KE9J91KMYQS0VZA38JDS2YRB</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Managing Table Entries</t>
+          <t>Location To Domain Table</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>h_01KE9JXR47N55S5V5CTRJQ4XSW</t>
+          <t>h_01KE9J91KMC68FBV8GSV3SW9P2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Candidates-to-Entra-ID-Integration-Guide/#h_01KE9JXR47N55S5V5CTRJQ4XSW</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Candidates-to-Entra-ID-Integration-Guide/#h_01KE9J91KMC68FBV8GSV3SW9P2</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Notes</t>
+          <t>Managing Table Entries</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -891,41 +891,41 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>h_01KE9JXR477CWB604Z7NPE7PKE</t>
+          <t>h_01KE9JXR47N55S5V5CTRJQ4XSW</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Candidates-to-Entra-ID-Integration-Guide/#h_01KE9JXR477CWB604Z7NPE7PKE</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Candidates-to-Entra-ID-Integration-Guide/#h_01KE9JXR47N55S5V5CTRJQ4XSW</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Notes</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>h_01K2F6D9Z78A59AB3KVE88H9G4</t>
+          <t>h_01KE9JXR477CWB604Z7NPE7PKE</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Candidates-to-Entra-ID-Integration-Guide/#h_01K2F6D9Z78A59AB3KVE88H9G4</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Candidates-to-Entra-ID-Integration-Guide/#h_01KE9JXR477CWB604Z7NPE7PKE</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Execute Integration</t>
+          <t>Schedule</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -935,129 +935,129 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>h_01K2F6DEXBP5A1KHTZSA3FMCQV</t>
+          <t>h_01K2F6D9Z78A59AB3KVE88H9G4</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Candidates-to-Entra-ID-Integration-Guide/#h_01K2F6DEXBP5A1KHTZSA3FMCQV</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Candidates-to-Entra-ID-Integration-Guide/#h_01K2F6D9Z78A59AB3KVE88H9G4</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Additional Options</t>
+          <t>Execute Integration</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H1</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>h_01K2F6DMW23YJJ84ZW61QNFA00</t>
+          <t>h_01K2F6DEXBP5A1KHTZSA3FMCQV</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Candidates-to-Entra-ID-Integration-Guide/#h_01K2F6DMW23YJJ84ZW61QNFA00</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Candidates-to-Entra-ID-Integration-Guide/#h_01K2F6DEXBP5A1KHTZSA3FMCQV</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Appendix</t>
+          <t>Additional Options</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>h_01K6DA5S7RW3ZAKNHTAWBJZNSE</t>
+          <t>h_01K2F6DMW23YJJ84ZW61QNFA00</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Candidates-to-Entra-ID-Integration-Guide/#h_01K6DA5S7RW3ZAKNHTAWBJZNSE</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Candidates-to-Entra-ID-Integration-Guide/#h_01K2F6DMW23YJJ84ZW61QNFA00</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Permissions Required for Fetching the Candidate and Recruiting Report</t>
+          <t>Appendix</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H1</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>h_01K8TAT51GD6WTHVN3STMPVVYD</t>
+          <t>h_01K6DA5S7RW3ZAKNHTAWBJZNSE</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Candidates-to-Entra-ID-Integration-Guide/#h_01K8TAT51GD6WTHVN3STMPVVYD</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Candidates-to-Entra-ID-Integration-Guide/#h_01K6DA5S7RW3ZAKNHTAWBJZNSE</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Access the Integration Role</t>
+          <t>Permissions Required for Fetching the Candidate and Recruiting Report</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>h_01K8TGZKB7G6W079HTZAEXJTF9</t>
+          <t>h_01K8TAT51GD6WTHVN3STMPVVYD</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Candidates-to-Entra-ID-Integration-Guide/#h_01K8TGZKB7G6W079HTZAEXJTF9</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Candidates-to-Entra-ID-Integration-Guide/#h_01K8TAT51GD6WTHVN3STMPVVYD</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Analytics</t>
+          <t>Access the Integration Role</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>h_01K8TG1ST1GG3FYK5V8NA2QPF5</t>
+          <t>h_01K8TGZKB7G6W079HTZAEXJTF9</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Candidates-to-Entra-ID-Integration-Guide/#h_01K8TG1ST1GG3FYK5V8NA2QPF5</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Candidates-to-Entra-ID-Integration-Guide/#h_01K8TGZKB7G6W079HTZAEXJTF9</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>HCM Anywhere</t>
+          <t>Analytics</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1067,19 +1067,19 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>h_01K8TEAE549HWCQBK4MHCWTGX1</t>
+          <t>h_01K8TG1ST1GG3FYK5V8NA2QPF5</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Candidates-to-Entra-ID-Integration-Guide/#h_01K8TEAE549HWCQBK4MHCWTGX1</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Candidates-to-Entra-ID-Integration-Guide/#h_01K8TG1ST1GG3FYK5V8NA2QPF5</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Recruiting</t>
+          <t>HCM Anywhere</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1089,19 +1089,19 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>h_01K8TEAE542GRDM6T6YGXTTVH9</t>
+          <t>h_01K8TEAE549HWCQBK4MHCWTGX1</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Candidates-to-Entra-ID-Integration-Guide/#h_01K8TEAE542GRDM6T6YGXTTVH9</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Candidates-to-Entra-ID-Integration-Guide/#h_01K8TEAE549HWCQBK4MHCWTGX1</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Reporting and Analytics</t>
+          <t>Recruiting</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1111,41 +1111,41 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>h_01K8TF92W7W8B369S0BKVZDB5M</t>
+          <t>h_01K8TEAE542GRDM6T6YGXTTVH9</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Candidates-to-Entra-ID-Integration-Guide/#h_01K8TF92W7W8B369S0BKVZDB5M</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Candidates-to-Entra-ID-Integration-Guide/#h_01K8TEAE542GRDM6T6YGXTTVH9</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Set Authorization Permissions</t>
+          <t>Reporting and Analytics</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>h_01K8TAT51GM5T9EB2K19A8ASN0</t>
+          <t>h_01K8TF92W7W8B369S0BKVZDB5M</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Candidates-to-Entra-ID-Integration-Guide/#h_01K8TAT51GM5T9EB2K19A8ASN0</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Candidates-to-Entra-ID-Integration-Guide/#h_01K8TF92W7W8B369S0BKVZDB5M</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Verify Role Configuration</t>
+          <t>Set Authorization Permissions</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1155,19 +1155,19 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>h_01K8TH4GTX8WJS2YS2R1FXWGX3</t>
+          <t>h_01K8TAT51GM5T9EB2K19A8ASN0</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Candidates-to-Entra-ID-Integration-Guide/#h_01K8TH4GTX8WJS2YS2R1FXWGX3</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Candidates-to-Entra-ID-Integration-Guide/#h_01K8TAT51GM5T9EB2K19A8ASN0</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Set Web Services Field-Level Access</t>
+          <t>Verify Role Configuration</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1177,41 +1177,41 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>h_01K9SAZF7D05D7KWVD3SQK6WF2</t>
+          <t>h_01K8TH4GTX8WJS2YS2R1FXWGX3</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Candidates-to-Entra-ID-Integration-Guide/#h_01K9SAZF7D05D7KWVD3SQK6WF2</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Candidates-to-Entra-ID-Integration-Guide/#h_01K8TH4GTX8WJS2YS2R1FXWGX3</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Creating Candidate Report</t>
+          <t>Set Web Services Field-Level Access</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>h_01K6D9458MNC1FCP1F05RC3P59</t>
+          <t>h_01K9SAZF7D05D7KWVD3SQK6WF2</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Candidates-to-Entra-ID-Integration-Guide/#h_01K6D9458MNC1FCP1F05RC3P59</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Candidates-to-Entra-ID-Integration-Guide/#h_01K9SAZF7D05D7KWVD3SQK6WF2</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Permissions Required for Application Access to Candidate and Recruiting Data</t>
+          <t>Creating Candidate Report</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1221,32 +1221,54 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>h_01K8TKEAZVQFSXSSNABJ4QRKVE</t>
+          <t>h_01K6D9458MNC1FCP1F05RC3P59</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Candidates-to-Entra-ID-Integration-Guide/#h_01K8TKEAZVQFSXSSNABJ4QRKVE</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Candidates-to-Entra-ID-Integration-Guide/#h_01K6D9458MNC1FCP1F05RC3P59</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
+          <t>Permissions Required for Application Access to Candidate and Recruiting Data</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>h_01K8TKEAZVQFSXSSNABJ4QRKVE</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Candidates-to-Entra-ID-Integration-Guide/#h_01K8TKEAZVQFSXSSNABJ4QRKVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
           <t>Mandatory Attributes for Integration</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>H2</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="C39" t="inlineStr">
         <is>
           <t>h_01K6MS9V5D4KXH90F4V8C167TD</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="D39" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Candidates-to-Entra-ID-Integration-Guide/#h_01K6MS9V5D4KXH90F4V8C167TD</t>
         </is>
